--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404F43D4-BB95-4EB6-A6E9-B97D4BD80F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA08842-7E45-49BF-B0B7-4F25EEF45C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -230,6 +230,21 @@
   </si>
   <si>
     <t>CREATING OWN RECORD</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>REST DAY</t>
+  </si>
+  <si>
+    <t>FIGURING OUT THINGS</t>
+  </si>
+  <si>
+    <t>INITIAL PICK UP</t>
+  </si>
+  <si>
+    <t>CONTINUING IN PAIN</t>
   </si>
 </sst>
 </file>
@@ -1272,93 +1287,189 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+    <row r="11" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="18">
+        <v>46257</v>
+      </c>
+      <c r="B11" s="20">
+        <v>720</v>
+      </c>
+      <c r="C11" s="20">
+        <v>50</v>
+      </c>
+      <c r="D11" s="20">
+        <v>280</v>
+      </c>
+      <c r="E11" s="20">
+        <v>20</v>
+      </c>
+      <c r="F11" s="20">
+        <v>0</v>
+      </c>
+      <c r="G11" s="20">
+        <v>0</v>
+      </c>
+      <c r="H11" s="20">
+        <v>30</v>
+      </c>
+      <c r="I11" s="19">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J11" s="19">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+        <v>340</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="M11" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N11" s="22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="18">
+        <v>46258</v>
+      </c>
+      <c r="B12" s="20">
+        <v>420</v>
+      </c>
+      <c r="C12" s="20">
+        <v>100</v>
+      </c>
+      <c r="D12" s="20">
+        <v>120</v>
+      </c>
+      <c r="E12" s="20">
+        <v>150</v>
+      </c>
+      <c r="F12" s="20">
+        <v>250</v>
+      </c>
+      <c r="G12" s="20">
+        <v>5</v>
+      </c>
+      <c r="H12" s="20">
+        <v>30</v>
+      </c>
+      <c r="I12" s="19">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J12" s="19">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+        <v>370</v>
+      </c>
+      <c r="K12" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" s="22" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="18">
+        <v>46259</v>
+      </c>
+      <c r="B13" s="20">
+        <v>300</v>
+      </c>
+      <c r="C13" s="20">
+        <v>50</v>
+      </c>
+      <c r="D13" s="20">
+        <v>180</v>
+      </c>
+      <c r="E13" s="20">
+        <v>50</v>
+      </c>
+      <c r="F13" s="20">
+        <v>300</v>
+      </c>
+      <c r="G13" s="20">
+        <v>6</v>
+      </c>
+      <c r="H13" s="20">
+        <v>100</v>
+      </c>
+      <c r="I13" s="19">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J13" s="19">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+        <v>460</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="18">
+        <v>46260</v>
+      </c>
+      <c r="B14" s="20">
+        <v>330</v>
+      </c>
+      <c r="C14" s="20">
+        <v>180</v>
+      </c>
+      <c r="D14" s="20">
+        <v>160</v>
+      </c>
+      <c r="E14" s="20">
+        <v>100</v>
+      </c>
+      <c r="F14" s="20">
+        <v>300</v>
+      </c>
+      <c r="G14" s="20">
+        <v>6</v>
+      </c>
+      <c r="H14" s="20">
+        <v>100</v>
+      </c>
+      <c r="I14" s="19">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J14" s="19">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K14" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="N14" s="22" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA08842-7E45-49BF-B0B7-4F25EEF45C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{968BC972-1347-4376-A89A-2783BF4F2ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>CONTINUING IN PAIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRYING TO PICK UP </t>
   </si>
 </sst>
 </file>
@@ -1471,27 +1474,51 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+    <row r="15" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="18">
+        <v>46261</v>
+      </c>
+      <c r="B15" s="20">
+        <v>480</v>
+      </c>
+      <c r="C15" s="20">
+        <v>120</v>
+      </c>
+      <c r="D15" s="20">
+        <v>180</v>
+      </c>
+      <c r="E15" s="20">
+        <v>120</v>
+      </c>
+      <c r="F15" s="20">
+        <v>300</v>
+      </c>
+      <c r="G15" s="20">
+        <v>6</v>
+      </c>
+      <c r="H15" s="20">
+        <v>30</v>
+      </c>
+      <c r="I15" s="19">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J15" s="19">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>210</v>
+      </c>
+      <c r="K15" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="22" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2ADFAD9-4BFB-4595-BBEF-70A895171DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD174BF-F43E-4D3A-BC16-4B9BECFDBB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>BRINGING POSITIVITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> GOOD CONSISTENCY</t>
   </si>
 </sst>
 </file>
@@ -1549,26 +1552,50 @@
       </c>
     </row>
     <row r="17" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="14" t="str">
+      <c r="A17" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B17" s="15">
+        <v>300</v>
+      </c>
+      <c r="C17" s="15">
+        <v>120</v>
+      </c>
+      <c r="D17" s="15">
+        <v>420</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0</v>
+      </c>
+      <c r="F17" s="15">
+        <v>0</v>
+      </c>
+      <c r="G17" s="15">
+        <v>0</v>
+      </c>
+      <c r="H17" s="15">
+        <v>30</v>
+      </c>
+      <c r="I17" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="14" t="str">
+        <v>870</v>
+      </c>
+      <c r="J17" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="18" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD174BF-F43E-4D3A-BC16-4B9BECFDBB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBDC4EB-A6F5-4965-B120-A5F5F8C424D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t xml:space="preserve"> GOOD CONSISTENCY</t>
+  </si>
+  <si>
+    <t>DOING GOOD</t>
   </si>
 </sst>
 </file>
@@ -1598,26 +1601,50 @@
       </c>
     </row>
     <row r="18" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="13"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="14" t="str">
+      <c r="A18" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B18" s="15">
+        <v>540</v>
+      </c>
+      <c r="C18" s="15">
+        <v>30</v>
+      </c>
+      <c r="D18" s="15">
+        <v>300</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0</v>
+      </c>
+      <c r="F18" s="15">
+        <v>0</v>
+      </c>
+      <c r="G18" s="15">
+        <v>0</v>
+      </c>
+      <c r="H18" s="15">
+        <v>20</v>
+      </c>
+      <c r="I18" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="14" t="str">
+        <v>890</v>
+      </c>
+      <c r="J18" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="19" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBDC4EB-A6F5-4965-B120-A5F5F8C424D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0C19F8-E907-4AEE-95CB-409F3EF69453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t>DOING GOOD</t>
+  </si>
+  <si>
+    <t>SURVIVING MINDSET</t>
   </si>
 </sst>
 </file>
@@ -1647,26 +1650,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="14" t="str">
+      <c r="A19" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B19" s="15">
+        <v>320</v>
+      </c>
+      <c r="C19" s="15">
+        <v>50</v>
+      </c>
+      <c r="D19" s="15">
+        <v>120</v>
+      </c>
+      <c r="E19" s="15">
+        <v>120</v>
+      </c>
+      <c r="F19" s="15">
+        <v>250</v>
+      </c>
+      <c r="G19" s="15">
+        <v>5</v>
+      </c>
+      <c r="H19" s="15">
+        <v>10</v>
+      </c>
+      <c r="I19" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="14" t="str">
+        <v>870</v>
+      </c>
+      <c r="J19" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="20" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0C19F8-E907-4AEE-95CB-409F3EF69453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA4E0FE-5447-443F-906C-2B4400E20D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -260,6 +260,9 @@
   </si>
   <si>
     <t>SURVIVING MINDSET</t>
+  </si>
+  <si>
+    <t>GOING WELL</t>
   </si>
 </sst>
 </file>
@@ -1696,26 +1699,50 @@
       </c>
     </row>
     <row r="20" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="13"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="14" t="str">
+      <c r="A20" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B20" s="15">
+        <v>480</v>
+      </c>
+      <c r="C20" s="15">
+        <v>20</v>
+      </c>
+      <c r="D20" s="15">
+        <v>120</v>
+      </c>
+      <c r="E20" s="15">
+        <v>100</v>
+      </c>
+      <c r="F20" s="15">
+        <v>300</v>
+      </c>
+      <c r="G20" s="15">
+        <v>6</v>
+      </c>
+      <c r="H20" s="15">
+        <v>120</v>
+      </c>
+      <c r="I20" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="14" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J20" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="21" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA4E0FE-5447-443F-906C-2B4400E20D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BAA133-18B0-4A4B-810B-39D66C6C0AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>GOING WELL</t>
+  </si>
+  <si>
+    <t>NOT LEAVING TO TRY</t>
   </si>
 </sst>
 </file>
@@ -1745,26 +1748,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="13"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="14" t="str">
+      <c r="A21" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B21" s="15">
+        <v>460</v>
+      </c>
+      <c r="C21" s="15">
+        <v>30</v>
+      </c>
+      <c r="D21" s="15">
+        <v>110</v>
+      </c>
+      <c r="E21" s="15">
+        <v>100</v>
+      </c>
+      <c r="F21" s="15">
+        <v>300</v>
+      </c>
+      <c r="G21" s="15">
+        <v>6</v>
+      </c>
+      <c r="H21" s="15">
+        <v>20</v>
+      </c>
+      <c r="I21" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="14" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J21" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="22" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BAA133-18B0-4A4B-810B-39D66C6C0AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D0ED7A-B57D-4DD2-A1CF-2B8867EF7D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>NOT LEAVING TO TRY</t>
+  </si>
+  <si>
+    <t>HOPE NEVER FADES</t>
   </si>
 </sst>
 </file>
@@ -1794,26 +1797,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="13"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="14" t="str">
+      <c r="A22" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B22" s="15">
+        <v>540</v>
+      </c>
+      <c r="C22" s="15">
+        <v>0</v>
+      </c>
+      <c r="D22" s="15">
+        <v>180</v>
+      </c>
+      <c r="E22" s="15">
+        <v>100</v>
+      </c>
+      <c r="F22" s="15">
+        <v>300</v>
+      </c>
+      <c r="G22" s="15">
+        <v>6</v>
+      </c>
+      <c r="H22" s="15">
+        <v>0</v>
+      </c>
+      <c r="I22" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="14" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J22" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="23" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D0ED7A-B57D-4DD2-A1CF-2B8867EF7D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFEF103E-ED84-4186-AEE0-C12AC7571D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t>HOPE NEVER FADES</t>
+  </si>
+  <si>
+    <t>SURVIVING THE DAY</t>
   </si>
 </sst>
 </file>
@@ -1843,26 +1846,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="13"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="14" t="str">
+      <c r="A23" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B23" s="15">
+        <v>480</v>
+      </c>
+      <c r="C23" s="15">
+        <v>0</v>
+      </c>
+      <c r="D23" s="15">
+        <v>200</v>
+      </c>
+      <c r="E23" s="15">
+        <v>0</v>
+      </c>
+      <c r="F23" s="15">
+        <v>250</v>
+      </c>
+      <c r="G23" s="15">
+        <v>5</v>
+      </c>
+      <c r="H23" s="15">
+        <v>0</v>
+      </c>
+      <c r="I23" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="14" t="str">
+        <v>930</v>
+      </c>
+      <c r="J23" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="24" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFEF103E-ED84-4186-AEE0-C12AC7571D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42EE76D5-CF79-4BD6-989D-C974E7335B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>SURVIVING THE DAY</t>
+  </si>
+  <si>
+    <t>ADJUSTING MYSELF</t>
   </si>
 </sst>
 </file>
@@ -1892,26 +1895,50 @@
       </c>
     </row>
     <row r="24" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="13"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="14" t="str">
+      <c r="A24" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B24" s="15">
+        <v>450</v>
+      </c>
+      <c r="C24" s="15">
+        <v>0</v>
+      </c>
+      <c r="D24" s="15">
+        <v>420</v>
+      </c>
+      <c r="E24" s="15">
+        <v>0</v>
+      </c>
+      <c r="F24" s="15">
+        <v>0</v>
+      </c>
+      <c r="G24" s="15">
+        <v>0</v>
+      </c>
+      <c r="H24" s="15">
+        <v>20</v>
+      </c>
+      <c r="I24" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="14" t="str">
+        <v>890</v>
+      </c>
+      <c r="J24" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="25" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A25" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42EE76D5-CF79-4BD6-989D-C974E7335B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DEF65F1-3A4B-4464-A183-DEBC5B9ED8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>ADJUSTING MYSELF</t>
+  </si>
+  <si>
+    <t>BORING DAY</t>
   </si>
 </sst>
 </file>
@@ -1941,26 +1944,50 @@
       </c>
     </row>
     <row r="25" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="14" t="str">
+      <c r="A25" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B25" s="15">
+        <v>480</v>
+      </c>
+      <c r="C25" s="15">
+        <v>0</v>
+      </c>
+      <c r="D25" s="15">
+        <v>300</v>
+      </c>
+      <c r="E25" s="15">
+        <v>0</v>
+      </c>
+      <c r="F25" s="15">
+        <v>0</v>
+      </c>
+      <c r="G25" s="15">
+        <v>0</v>
+      </c>
+      <c r="H25" s="15">
+        <v>20</v>
+      </c>
+      <c r="I25" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="14" t="str">
+        <v>800</v>
+      </c>
+      <c r="J25" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="26" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DEF65F1-3A4B-4464-A183-DEBC5B9ED8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B0CDAB-BD31-4E5E-83D3-F0A2E4C800A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>BORING DAY</t>
+  </si>
+  <si>
+    <t>ENJOYING EVERTHING</t>
   </si>
 </sst>
 </file>
@@ -1990,26 +1993,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="13"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="14" t="str">
+      <c r="A26" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B26" s="15">
+        <v>540</v>
+      </c>
+      <c r="C26" s="15">
+        <v>120</v>
+      </c>
+      <c r="D26" s="15">
+        <v>50</v>
+      </c>
+      <c r="E26" s="15">
+        <v>150</v>
+      </c>
+      <c r="F26" s="15">
+        <v>250</v>
+      </c>
+      <c r="G26" s="15">
+        <v>5</v>
+      </c>
+      <c r="H26" s="15">
+        <v>0</v>
+      </c>
+      <c r="I26" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="14" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J26" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="27" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A27" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B0CDAB-BD31-4E5E-83D3-F0A2E4C800A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC07498-DC61-4D16-B6F8-AF14470279E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>ENJOYING EVERTHING</t>
+  </si>
+  <si>
+    <t>LOST STILL LAUGHING</t>
   </si>
 </sst>
 </file>
@@ -2039,26 +2042,50 @@
       </c>
     </row>
     <row r="27" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="13"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="14" t="str">
+      <c r="A27" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B27" s="15">
+        <v>240</v>
+      </c>
+      <c r="C27" s="15">
+        <v>120</v>
+      </c>
+      <c r="D27" s="15">
+        <v>30</v>
+      </c>
+      <c r="E27" s="15">
+        <v>100</v>
+      </c>
+      <c r="F27" s="15">
+        <v>300</v>
+      </c>
+      <c r="G27" s="15">
+        <v>6</v>
+      </c>
+      <c r="H27" s="15">
+        <v>60</v>
+      </c>
+      <c r="I27" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="14" t="str">
+        <v>850</v>
+      </c>
+      <c r="J27" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>590</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="28" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC07498-DC61-4D16-B6F8-AF14470279E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D28E9E-C508-436E-9BFE-170399FAFE47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>LOST STILL LAUGHING</t>
+  </si>
+  <si>
+    <t>SLOWLY  RISING</t>
   </si>
 </sst>
 </file>
@@ -2088,26 +2091,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="13"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="14" t="str">
+      <c r="A28" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B28" s="15">
+        <v>390</v>
+      </c>
+      <c r="C28" s="15">
+        <v>120</v>
+      </c>
+      <c r="D28" s="15">
+        <v>120</v>
+      </c>
+      <c r="E28" s="15">
+        <v>100</v>
+      </c>
+      <c r="F28" s="15">
+        <v>300</v>
+      </c>
+      <c r="G28" s="15">
+        <v>6</v>
+      </c>
+      <c r="H28" s="15">
+        <v>10</v>
+      </c>
+      <c r="I28" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="14" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J28" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="29" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D28E9E-C508-436E-9BFE-170399FAFE47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC8D9E3B-BC24-4B30-8A2D-F1BC626FD77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -287,6 +287,9 @@
   </si>
   <si>
     <t>SLOWLY  RISING</t>
+  </si>
+  <si>
+    <t>THINKING TOO MUCH</t>
   </si>
 </sst>
 </file>
@@ -2137,26 +2140,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="13"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="14" t="str">
+      <c r="A29" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B29" s="15">
+        <v>270</v>
+      </c>
+      <c r="C29" s="15">
+        <v>120</v>
+      </c>
+      <c r="D29" s="15">
+        <v>0</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
+      </c>
+      <c r="F29" s="15">
+        <v>100</v>
+      </c>
+      <c r="G29" s="15">
+        <v>2</v>
+      </c>
+      <c r="H29" s="15">
+        <v>10</v>
+      </c>
+      <c r="I29" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="14" t="str">
+        <v>500</v>
+      </c>
+      <c r="J29" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>940</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="30" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC8D9E3B-BC24-4B30-8A2D-F1BC626FD77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E50393-77F5-4195-AFD4-7A79DFEF5BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>THINKING TOO MUCH</t>
+  </si>
+  <si>
+    <t>STARTED HASTY</t>
   </si>
 </sst>
 </file>
@@ -2186,26 +2189,50 @@
       </c>
     </row>
     <row r="30" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="13"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="14" t="str">
+      <c r="A30" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B30" s="15">
+        <v>280</v>
+      </c>
+      <c r="C30" s="15">
+        <v>120</v>
+      </c>
+      <c r="D30" s="15">
+        <v>50</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
+      </c>
+      <c r="F30" s="15">
+        <v>200</v>
+      </c>
+      <c r="G30" s="15">
+        <v>4</v>
+      </c>
+      <c r="H30" s="15">
+        <v>0</v>
+      </c>
+      <c r="I30" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="14" t="str">
+        <v>650</v>
+      </c>
+      <c r="J30" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>790</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="31" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A31" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E50393-77F5-4195-AFD4-7A79DFEF5BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1069DC7A-E455-4287-B612-71418CC296EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>STARTED HASTY</t>
+  </si>
+  <si>
+    <t>HAPPY FAMILY TIME</t>
   </si>
 </sst>
 </file>
@@ -2235,26 +2238,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="13"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="14" t="str">
+      <c r="A31" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B31" s="15">
+        <v>540</v>
+      </c>
+      <c r="C31" s="15">
+        <v>0</v>
+      </c>
+      <c r="D31" s="15">
+        <v>60</v>
+      </c>
+      <c r="E31" s="15">
+        <v>60</v>
+      </c>
+      <c r="F31" s="15">
+        <v>0</v>
+      </c>
+      <c r="G31" s="15">
+        <v>0</v>
+      </c>
+      <c r="H31" s="15">
+        <v>50</v>
+      </c>
+      <c r="I31" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="14" t="str">
+        <v>710</v>
+      </c>
+      <c r="J31" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>730</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="32" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A32" s="13"/>
